--- a/mlef_pipeline/results/OS_24/HIGH_PDL1/RWD/results.xlsx
+++ b/mlef_pipeline/results/OS_24/HIGH_PDL1/RWD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.58 ± 0.13</t>
+          <t>0.57 ± 0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.14</t>
+          <t>0.60 ± 0.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.67 ± 0.22</t>
+          <t>0.65 ± 0.22</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.79 ± 0.15</t>
+          <t>0.79 ± 0.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.64 ± 0.14</t>
+          <t>0.63 ± 0.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
